--- a/Data/Data-ETFPESOV.xlsx
+++ b/Data/Data-ETFPESOV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fernando\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6997545-5633-49A0-BA41-BC5B2F0AB0FB}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACF7903-26FA-4BAE-A813-D53DE119A5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Fecha</t>
   </si>
@@ -138,7 +138,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -515,13 +515,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AD359"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <dimension ref="A1:AD360"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="24" max="27" width="11.5" style="3"/>
+    <col min="24" max="27" width="11.5546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -613,7 +613,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45748</v>
       </c>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45749</v>
       </c>
@@ -725,7 +725,7 @@
         <v>1.2143671677051771E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45750</v>
       </c>
@@ -784,7 +784,7 @@
         <v>9.1175034119250764E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45751</v>
       </c>
@@ -843,7 +843,7 @@
         <v>1.1159691476292588E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45754</v>
       </c>
@@ -902,7 +902,7 @@
         <v>1.3318351860941879E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45755</v>
       </c>
@@ -961,7 +961,7 @@
         <v>1.4496105894190592E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45756</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>1.059531283173043E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45757</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9.5170229436190024E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45758</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>1.2588309241094331E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45761</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>3.6875895667234371E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45762</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>4.4103347852244568E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45763</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>1.069542784982902E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45768</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>3.2775521211678704E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45769</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>8.2411514863298674E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45770</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>9.8259889689884528E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:28">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>45771</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>6.1477814565573663E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:28">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>45772</v>
       </c>
@@ -1610,7 +1610,7 @@
         <v>7.6715295615414902E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:28">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>45775</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>6.3277755685609005E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:28">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>45776</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>2.1853312366791888E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:28">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>45777</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>5.0849546986864169E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:28">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>45779</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>5.3071721745676648E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:28">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>45782</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>1.5255835720811017E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:28">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>45783</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>7.5744419926038198E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:28">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>45784</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>3.3848643678949797E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:28">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>45785</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>2.6257951324997197E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:28">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>45786</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>5.2926816086399375E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:28">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>45789</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>3.0927042456607712E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:28">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>45790</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>6.1827320898003579E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:28">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45791</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>5.6980368512211665E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:28">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>45792</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>10502.5</v>
       </c>
     </row>
-    <row r="32" spans="1:28">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45793</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>9670</v>
       </c>
     </row>
-    <row r="33" spans="1:28">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>45796</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>9670</v>
       </c>
     </row>
-    <row r="34" spans="1:28">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>45797</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>9670</v>
       </c>
     </row>
-    <row r="35" spans="1:28">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>45798</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>9151.625</v>
       </c>
     </row>
-    <row r="36" spans="1:28">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>45799</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>8644.5</v>
       </c>
     </row>
-    <row r="37" spans="1:28">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>45800</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>7933</v>
       </c>
     </row>
-    <row r="38" spans="1:28">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>45803</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>7933</v>
       </c>
     </row>
-    <row r="39" spans="1:28">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>45804</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>7645.5</v>
       </c>
     </row>
-    <row r="40" spans="1:28">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>45805</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>7645.5</v>
       </c>
     </row>
-    <row r="41" spans="1:28">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45806</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>7645.5</v>
       </c>
     </row>
-    <row r="42" spans="1:28">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45807</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>7498.4</v>
       </c>
     </row>
-    <row r="43" spans="1:28">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45810</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>7498.4</v>
       </c>
     </row>
-    <row r="44" spans="1:28">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45811</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>7645.5</v>
       </c>
     </row>
-    <row r="45" spans="1:28">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45812</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>7498.4</v>
       </c>
     </row>
-    <row r="46" spans="1:28">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45813</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>7498.4</v>
       </c>
     </row>
-    <row r="47" spans="1:28">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45814</v>
       </c>
@@ -3522,7 +3522,7 @@
         <v>7293.4</v>
       </c>
     </row>
-    <row r="48" spans="1:28">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45817</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>7134.1</v>
       </c>
     </row>
-    <row r="49" spans="1:29">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45818</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>7293.4</v>
       </c>
     </row>
-    <row r="50" spans="1:29">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45819</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>7134.1</v>
       </c>
     </row>
-    <row r="51" spans="1:29">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45820</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>7134.1</v>
       </c>
     </row>
-    <row r="52" spans="1:29">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45821</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>7134.1</v>
       </c>
     </row>
-    <row r="53" spans="1:29">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45824</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>7293.4</v>
       </c>
     </row>
-    <row r="54" spans="1:29">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>45825</v>
       </c>
@@ -4019,7 +4019,7 @@
         <v>7293.4</v>
       </c>
     </row>
-    <row r="55" spans="1:29">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45826</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>7293.4</v>
       </c>
     </row>
-    <row r="56" spans="1:29">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>45827</v>
       </c>
@@ -4161,7 +4161,7 @@
         <v>7454.7749999999996</v>
       </c>
     </row>
-    <row r="57" spans="1:29">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>45828</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>7293.4</v>
       </c>
     </row>
-    <row r="58" spans="1:29">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45831</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>7310.0249999999996</v>
       </c>
     </row>
-    <row r="59" spans="1:29">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45832</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>7310.0249999999996</v>
       </c>
     </row>
-    <row r="60" spans="1:29">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>45833</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>7310.0249999999996</v>
       </c>
     </row>
-    <row r="61" spans="1:29">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>45834</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>7645.5</v>
       </c>
     </row>
-    <row r="62" spans="1:29">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>45835</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>7541.375</v>
       </c>
     </row>
-    <row r="63" spans="1:29">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>45838</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>7541.375</v>
       </c>
     </row>
-    <row r="64" spans="1:29">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>45839</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>7454.7749999999996</v>
       </c>
     </row>
-    <row r="65" spans="1:29">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>45840</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>7310.0249999999996</v>
       </c>
     </row>
-    <row r="66" spans="1:29">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>45841</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>7310.0249999999996</v>
       </c>
     </row>
-    <row r="67" spans="1:29">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>45842</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>7191.625</v>
       </c>
     </row>
-    <row r="68" spans="1:29">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>45845</v>
       </c>
@@ -5106,7 +5106,7 @@
         <v>7134.1</v>
       </c>
     </row>
-    <row r="69" spans="1:29">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>45846</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>7040.1</v>
       </c>
     </row>
-    <row r="70" spans="1:29">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>45847</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>7040.1</v>
       </c>
     </row>
-    <row r="71" spans="1:29">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>45848</v>
       </c>
@@ -5355,7 +5355,7 @@
         <v>7040.1</v>
       </c>
     </row>
-    <row r="72" spans="1:29">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>45849</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>6942</v>
       </c>
     </row>
-    <row r="73" spans="1:29">
+    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>45852</v>
       </c>
@@ -5521,7 +5521,7 @@
         <v>6942</v>
       </c>
     </row>
-    <row r="74" spans="1:29">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>45853</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>7040.1</v>
       </c>
     </row>
-    <row r="75" spans="1:29">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>45854</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>6942</v>
       </c>
     </row>
-    <row r="76" spans="1:29">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>45855</v>
       </c>
@@ -5770,7 +5770,7 @@
         <v>6942</v>
       </c>
     </row>
-    <row r="77" spans="1:29">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>45856</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>6852.875</v>
       </c>
     </row>
-    <row r="78" spans="1:29">
+    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>45859</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>6737.7350000000006</v>
       </c>
     </row>
-    <row r="79" spans="1:29">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>45860</v>
       </c>
@@ -6019,7 +6019,7 @@
         <v>6737.7350000000006</v>
       </c>
     </row>
-    <row r="80" spans="1:29">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>45862</v>
       </c>
@@ -6102,7 +6102,7 @@
         <v>6737.7350000000006</v>
       </c>
     </row>
-    <row r="81" spans="1:29">
+    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>45863</v>
       </c>
@@ -6185,7 +6185,7 @@
         <v>6737.7350000000006</v>
       </c>
     </row>
-    <row r="82" spans="1:29">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>45868</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>6737.7350000000006</v>
       </c>
     </row>
-    <row r="83" spans="1:29">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>45869</v>
       </c>
@@ -6351,7 +6351,7 @@
         <v>6852.875</v>
       </c>
     </row>
-    <row r="84" spans="1:29">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>45870</v>
       </c>
@@ -6434,7 +6434,7 @@
         <v>6737.7350000000006</v>
       </c>
     </row>
-    <row r="85" spans="1:29">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>45873</v>
       </c>
@@ -6517,7 +6517,7 @@
         <v>6737.7350000000006</v>
       </c>
     </row>
-    <row r="86" spans="1:29">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>45874</v>
       </c>
@@ -6600,7 +6600,7 @@
         <v>6808.45</v>
       </c>
     </row>
-    <row r="87" spans="1:29">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>45876</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>6808.45</v>
       </c>
     </row>
-    <row r="88" spans="1:29">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>45877</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>6852.875</v>
       </c>
     </row>
-    <row r="89" spans="1:29">
+    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>45880</v>
       </c>
@@ -6849,7 +6849,7 @@
         <v>6942</v>
       </c>
     </row>
-    <row r="90" spans="1:29">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>45881</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>6852.875</v>
       </c>
     </row>
-    <row r="91" spans="1:29">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>45882</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>6808.45</v>
       </c>
     </row>
-    <row r="92" spans="1:29">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>45883</v>
       </c>
@@ -7098,7 +7098,7 @@
         <v>6808.45</v>
       </c>
     </row>
-    <row r="93" spans="1:29">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>45884</v>
       </c>
@@ -7181,7 +7181,7 @@
         <v>6737.4349999999995</v>
       </c>
     </row>
-    <row r="94" spans="1:29">
+    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>45887</v>
       </c>
@@ -7264,7 +7264,7 @@
         <v>6652.2350000000006</v>
       </c>
     </row>
-    <row r="95" spans="1:29">
+    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>45888</v>
       </c>
@@ -7347,7 +7347,7 @@
         <v>6652.2350000000006</v>
       </c>
     </row>
-    <row r="96" spans="1:29">
+    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>45889</v>
       </c>
@@ -7430,7 +7430,7 @@
         <v>6652.2350000000006</v>
       </c>
     </row>
-    <row r="97" spans="1:29">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>45890</v>
       </c>
@@ -7513,7 +7513,7 @@
         <v>6652.2350000000006</v>
       </c>
     </row>
-    <row r="98" spans="1:29">
+    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>45891</v>
       </c>
@@ -7596,7 +7596,7 @@
         <v>6652.2350000000006</v>
       </c>
     </row>
-    <row r="99" spans="1:29">
+    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>45894</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>6611.125</v>
       </c>
     </row>
-    <row r="100" spans="1:29">
+    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>45895</v>
       </c>
@@ -7762,7 +7762,7 @@
         <v>6625.6100000000006</v>
       </c>
     </row>
-    <row r="101" spans="1:29">
+    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>45896</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>6737.4349999999995</v>
       </c>
     </row>
-    <row r="102" spans="1:29">
+    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>45897</v>
       </c>
@@ -7928,7 +7928,7 @@
         <v>6737.4349999999995</v>
       </c>
     </row>
-    <row r="103" spans="1:29">
+    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>45898</v>
       </c>
@@ -8011,7 +8011,7 @@
         <v>6737.4349999999995</v>
       </c>
     </row>
-    <row r="104" spans="1:29">
+    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>45901</v>
       </c>
@@ -8094,7 +8094,7 @@
         <v>6737.4349999999995</v>
       </c>
     </row>
-    <row r="105" spans="1:29">
+    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>45902</v>
       </c>
@@ -8177,7 +8177,7 @@
         <v>6808.45</v>
       </c>
     </row>
-    <row r="106" spans="1:29">
+    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>45903</v>
       </c>
@@ -8260,7 +8260,7 @@
         <v>6808.45</v>
       </c>
     </row>
-    <row r="107" spans="1:29">
+    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>45904</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>6852.875</v>
       </c>
     </row>
-    <row r="108" spans="1:29">
+    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>45905</v>
       </c>
@@ -8426,7 +8426,7 @@
         <v>6942</v>
       </c>
     </row>
-    <row r="109" spans="1:29">
+    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>45908</v>
       </c>
@@ -8509,7 +8509,7 @@
         <v>6942</v>
       </c>
     </row>
-    <row r="110" spans="1:29">
+    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>45909</v>
       </c>
@@ -8592,7 +8592,7 @@
         <v>6991.5</v>
       </c>
     </row>
-    <row r="111" spans="1:29">
+    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>45910</v>
       </c>
@@ -8675,7 +8675,7 @@
         <v>7008.5</v>
       </c>
     </row>
-    <row r="112" spans="1:29">
+    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>45911</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>7008.5</v>
       </c>
     </row>
-    <row r="113" spans="1:29">
+    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>45912</v>
       </c>
@@ -8841,7 +8841,7 @@
         <v>7008.5</v>
       </c>
     </row>
-    <row r="114" spans="1:29">
+    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>45915</v>
       </c>
@@ -8924,7 +8924,7 @@
         <v>7066.25</v>
       </c>
     </row>
-    <row r="115" spans="1:29">
+    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>45916</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>7008.5</v>
       </c>
     </row>
-    <row r="116" spans="1:29">
+    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>45917</v>
       </c>
@@ -9090,7 +9090,7 @@
         <v>7008.5</v>
       </c>
     </row>
-    <row r="117" spans="1:29">
+    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>45918</v>
       </c>
@@ -9173,7 +9173,7 @@
         <v>7066.25</v>
       </c>
     </row>
-    <row r="118" spans="1:29">
+    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>45919</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>7008.5</v>
       </c>
     </row>
-    <row r="119" spans="1:29">
+    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>45922</v>
       </c>
@@ -9339,7 +9339,7 @@
         <v>7066.25</v>
       </c>
     </row>
-    <row r="120" spans="1:29">
+    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>45923</v>
       </c>
@@ -9422,7 +9422,7 @@
         <v>7008.5</v>
       </c>
     </row>
-    <row r="121" spans="1:29">
+    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>45924</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>7066.25</v>
       </c>
     </row>
-    <row r="122" spans="1:29">
+    <row r="122" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>45925</v>
       </c>
@@ -9588,7 +9588,7 @@
         <v>7210.75</v>
       </c>
     </row>
-    <row r="123" spans="1:29">
+    <row r="123" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>45926</v>
       </c>
@@ -9671,7 +9671,7 @@
         <v>7066.25</v>
       </c>
     </row>
-    <row r="124" spans="1:29">
+    <row r="124" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>45929</v>
       </c>
@@ -9754,7 +9754,7 @@
         <v>7210.75</v>
       </c>
     </row>
-    <row r="125" spans="1:29">
+    <row r="125" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>45930</v>
       </c>
@@ -9837,7 +9837,7 @@
         <v>7417.125</v>
       </c>
     </row>
-    <row r="126" spans="1:29">
+    <row r="126" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>45931</v>
       </c>
@@ -9920,7 +9920,7 @@
         <v>7210.75</v>
       </c>
     </row>
-    <row r="127" spans="1:29">
+    <row r="127" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>45932</v>
       </c>
@@ -10003,7 +10003,7 @@
         <v>7417.125</v>
       </c>
     </row>
-    <row r="128" spans="1:29">
+    <row r="128" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>45933</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>7525.25</v>
       </c>
     </row>
-    <row r="129" spans="1:29">
+    <row r="129" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>45936</v>
       </c>
@@ -10169,7 +10169,7 @@
         <v>7525.25</v>
       </c>
     </row>
-    <row r="130" spans="1:29">
+    <row r="130" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>45937</v>
       </c>
@@ -10252,7 +10252,7 @@
         <v>7525.25</v>
       </c>
     </row>
-    <row r="131" spans="1:29">
+    <row r="131" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>45939</v>
       </c>
@@ -10335,7 +10335,7 @@
         <v>7525.25</v>
       </c>
     </row>
-    <row r="132" spans="1:29">
+    <row r="132" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>45940</v>
       </c>
@@ -10418,7 +10418,7 @@
         <v>7525.25</v>
       </c>
     </row>
-    <row r="133" spans="1:29">
+    <row r="133" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>45943</v>
       </c>
@@ -10501,7 +10501,7 @@
         <v>7619.625</v>
       </c>
     </row>
-    <row r="134" spans="1:29">
+    <row r="134" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>45944</v>
       </c>
@@ -10584,7 +10584,7 @@
         <v>7618.625</v>
       </c>
     </row>
-    <row r="135" spans="1:29">
+    <row r="135" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>45945</v>
       </c>
@@ -10667,7 +10667,7 @@
         <v>7720</v>
       </c>
     </row>
-    <row r="136" spans="1:29">
+    <row r="136" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>45946</v>
       </c>
@@ -10750,7 +10750,7 @@
         <v>7720</v>
       </c>
     </row>
-    <row r="137" spans="1:29">
+    <row r="137" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>45947</v>
       </c>
@@ -10833,7 +10833,7 @@
         <v>7720</v>
       </c>
     </row>
-    <row r="138" spans="1:29">
+    <row r="138" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>45950</v>
       </c>
@@ -10916,7 +10916,7 @@
         <v>7720</v>
       </c>
     </row>
-    <row r="139" spans="1:29">
+    <row r="139" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>45951</v>
       </c>
@@ -10999,7 +10999,7 @@
         <v>7720</v>
       </c>
     </row>
-    <row r="140" spans="1:29">
+    <row r="140" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>45952</v>
       </c>
@@ -11082,7 +11082,7 @@
         <v>7720</v>
       </c>
     </row>
-    <row r="141" spans="1:29">
+    <row r="141" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>45953</v>
       </c>
@@ -11165,7 +11165,7 @@
         <v>7876</v>
       </c>
     </row>
-    <row r="142" spans="1:29">
+    <row r="142" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>45954</v>
       </c>
@@ -11248,7 +11248,7 @@
         <v>7900.5</v>
       </c>
     </row>
-    <row r="143" spans="1:29">
+    <row r="143" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>45957</v>
       </c>
@@ -11331,7 +11331,7 @@
         <v>7900.5</v>
       </c>
     </row>
-    <row r="144" spans="1:29">
+    <row r="144" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>45958</v>
       </c>
@@ -11414,7 +11414,7 @@
         <v>8071.1</v>
       </c>
     </row>
-    <row r="145" spans="1:29">
+    <row r="145" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>45959</v>
       </c>
@@ -11497,7 +11497,7 @@
         <v>8071.1</v>
       </c>
     </row>
-    <row r="146" spans="1:29">
+    <row r="146" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>45960</v>
       </c>
@@ -11580,7 +11580,7 @@
         <v>8071.1</v>
       </c>
     </row>
-    <row r="147" spans="1:29">
+    <row r="147" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>45961</v>
       </c>
@@ -11663,7 +11663,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="148" spans="1:29">
+    <row r="148" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>45964</v>
       </c>
@@ -11746,7 +11746,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="149" spans="1:29">
+    <row r="149" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>45965</v>
       </c>
@@ -11829,7 +11829,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="150" spans="1:29">
+    <row r="150" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>45966</v>
       </c>
@@ -11912,7 +11912,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="151" spans="1:29">
+    <row r="151" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>45967</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>8213.2000000000007</v>
       </c>
     </row>
-    <row r="152" spans="1:29">
+    <row r="152" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>45968</v>
       </c>
@@ -12078,7 +12078,7 @@
         <v>8213.2000000000007</v>
       </c>
     </row>
-    <row r="153" spans="1:29">
+    <row r="153" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>45971</v>
       </c>
@@ -12161,7 +12161,7 @@
         <v>8318.7999999999993</v>
       </c>
     </row>
-    <row r="154" spans="1:29">
+    <row r="154" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>45972</v>
       </c>
@@ -12244,7 +12244,7 @@
         <v>8397.2999999999993</v>
       </c>
     </row>
-    <row r="155" spans="1:29">
+    <row r="155" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>45973</v>
       </c>
@@ -12327,7 +12327,7 @@
         <v>8397.2999999999993</v>
       </c>
     </row>
-    <row r="156" spans="1:29">
+    <row r="156" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>45974</v>
       </c>
@@ -12410,7 +12410,7 @@
         <v>8397.2999999999993</v>
       </c>
     </row>
-    <row r="157" spans="1:29">
+    <row r="157" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>45975</v>
       </c>
@@ -12493,7 +12493,7 @@
         <v>8451.2000000000007</v>
       </c>
     </row>
-    <row r="158" spans="1:29">
+    <row r="158" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>45978</v>
       </c>
@@ -12576,7 +12576,7 @@
         <v>8451.2000000000007</v>
       </c>
     </row>
-    <row r="159" spans="1:29">
+    <row r="159" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>45979</v>
       </c>
@@ -12659,7 +12659,7 @@
         <v>8522.9</v>
       </c>
     </row>
-    <row r="160" spans="1:29">
+    <row r="160" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>45980</v>
       </c>
@@ -12742,7 +12742,7 @@
         <v>8482.9</v>
       </c>
     </row>
-    <row r="161" spans="1:29">
+    <row r="161" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>45981</v>
       </c>
@@ -12825,7 +12825,7 @@
         <v>8482.9</v>
       </c>
     </row>
-    <row r="162" spans="1:29">
+    <row r="162" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>45982</v>
       </c>
@@ -12908,7 +12908,7 @@
         <v>8482.9</v>
       </c>
     </row>
-    <row r="163" spans="1:29">
+    <row r="163" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>45985</v>
       </c>
@@ -12991,7 +12991,7 @@
         <v>8542</v>
       </c>
     </row>
-    <row r="164" spans="1:29">
+    <row r="164" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>45986</v>
       </c>
@@ -13074,7 +13074,7 @@
         <v>8542</v>
       </c>
     </row>
-    <row r="165" spans="1:29">
+    <row r="165" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>45987</v>
       </c>
@@ -13157,7 +13157,7 @@
         <v>8542</v>
       </c>
     </row>
-    <row r="166" spans="1:29">
+    <row r="166" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>45988</v>
       </c>
@@ -13240,7 +13240,7 @@
         <v>8542</v>
       </c>
     </row>
-    <row r="167" spans="1:29">
+    <row r="167" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>45989</v>
       </c>
@@ -13323,7 +13323,7 @@
         <v>8652.85</v>
       </c>
     </row>
-    <row r="168" spans="1:29">
+    <row r="168" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>45992</v>
       </c>
@@ -13406,7 +13406,7 @@
         <v>8652.85</v>
       </c>
     </row>
-    <row r="169" spans="1:29">
+    <row r="169" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>45993</v>
       </c>
@@ -13489,7 +13489,7 @@
         <v>8652.85</v>
       </c>
     </row>
-    <row r="170" spans="1:29">
+    <row r="170" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>45994</v>
       </c>
@@ -13572,7 +13572,7 @@
         <v>8730</v>
       </c>
     </row>
-    <row r="171" spans="1:29">
+    <row r="171" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>45995</v>
       </c>
@@ -13655,7 +13655,7 @@
         <v>8730</v>
       </c>
     </row>
-    <row r="172" spans="1:29">
+    <row r="172" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>45996</v>
       </c>
@@ -13738,7 +13738,7 @@
         <v>8730</v>
       </c>
     </row>
-    <row r="173" spans="1:29">
+    <row r="173" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>46001</v>
       </c>
@@ -13821,7 +13821,7 @@
         <v>8730</v>
       </c>
     </row>
-    <row r="174" spans="1:29">
+    <row r="174" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>46002</v>
       </c>
@@ -13904,7 +13904,7 @@
         <v>8542</v>
       </c>
     </row>
-    <row r="175" spans="1:29">
+    <row r="175" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>46003</v>
       </c>
@@ -13987,7 +13987,7 @@
         <v>8730</v>
       </c>
     </row>
-    <row r="176" spans="1:29">
+    <row r="176" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>46006</v>
       </c>
@@ -14070,7 +14070,7 @@
         <v>8885.9</v>
       </c>
     </row>
-    <row r="177" spans="1:30">
+    <row r="177" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>46007</v>
       </c>
@@ -14153,7 +14153,7 @@
         <v>9733.4</v>
       </c>
     </row>
-    <row r="178" spans="1:30">
+    <row r="178" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>46008</v>
       </c>
@@ -14236,7 +14236,7 @@
         <v>10623.9</v>
       </c>
     </row>
-    <row r="179" spans="1:30">
+    <row r="179" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>46009</v>
       </c>
@@ -14319,7 +14319,7 @@
         <v>10623.9</v>
       </c>
     </row>
-    <row r="180" spans="1:30">
+    <row r="180" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>46010</v>
       </c>
@@ -14402,7 +14402,7 @@
         <v>10623.9</v>
       </c>
     </row>
-    <row r="181" spans="1:30">
+    <row r="181" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>46013</v>
       </c>
@@ -14491,7 +14491,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="182" spans="1:30">
+    <row r="182" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>46014</v>
       </c>
@@ -14583,7 +14583,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="183" spans="1:30">
+    <row r="183" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>46015</v>
       </c>
@@ -14675,7 +14675,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="184" spans="1:30">
+    <row r="184" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>46017</v>
       </c>
@@ -14767,7 +14767,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="185" spans="1:30">
+    <row r="185" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>46020</v>
       </c>
@@ -14859,7 +14859,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="186" spans="1:30">
+    <row r="186" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>46021</v>
       </c>
@@ -14951,7 +14951,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="187" spans="1:30">
+    <row r="187" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>46022</v>
       </c>
@@ -15043,7 +15043,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="188" spans="1:30">
+    <row r="188" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>46024</v>
       </c>
@@ -15135,7 +15135,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="189" spans="1:30">
+    <row r="189" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>46027</v>
       </c>
@@ -15227,7 +15227,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="190" spans="1:30">
+    <row r="190" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>46028</v>
       </c>
@@ -15319,7 +15319,7 @@
         <v>8152.4</v>
       </c>
     </row>
-    <row r="191" spans="1:30">
+    <row r="191" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>46029</v>
       </c>
@@ -15411,7 +15411,7 @@
         <v>8188.4250000000002</v>
       </c>
     </row>
-    <row r="192" spans="1:30">
+    <row r="192" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>46030</v>
       </c>
@@ -15503,7 +15503,7 @@
         <v>8188.4250000000002</v>
       </c>
     </row>
-    <row r="193" spans="1:30">
+    <row r="193" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>46031</v>
       </c>
@@ -15595,7 +15595,7 @@
         <v>8249.2250000000004</v>
       </c>
     </row>
-    <row r="194" spans="1:30">
+    <row r="194" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>46034</v>
       </c>
@@ -15687,7 +15687,7 @@
         <v>8318.7999999999993</v>
       </c>
     </row>
-    <row r="195" spans="1:30">
+    <row r="195" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>46035</v>
       </c>
@@ -15779,7 +15779,7 @@
         <v>8318.7999999999993</v>
       </c>
     </row>
-    <row r="196" spans="1:30">
+    <row r="196" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>46036</v>
       </c>
@@ -15871,7 +15871,7 @@
         <v>8318.7999999999993</v>
       </c>
     </row>
-    <row r="197" spans="1:30">
+    <row r="197" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>46037</v>
       </c>
@@ -15963,7 +15963,7 @@
         <v>8318.7999999999993</v>
       </c>
     </row>
-    <row r="198" spans="1:30">
+    <row r="198" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>46038</v>
       </c>
@@ -16055,7 +16055,7 @@
         <v>8318.7999999999993</v>
       </c>
     </row>
-    <row r="199" spans="1:30">
+    <row r="199" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>46041</v>
       </c>
@@ -16147,7 +16147,7 @@
         <v>8367.4249999999993</v>
       </c>
     </row>
-    <row r="200" spans="1:30">
+    <row r="200" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>46042</v>
       </c>
@@ -16239,7 +16239,7 @@
         <v>8408.7250000000004</v>
       </c>
     </row>
-    <row r="201" spans="1:30">
+    <row r="201" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>46043</v>
       </c>
@@ -16331,7 +16331,7 @@
         <v>8451.2000000000007</v>
       </c>
     </row>
-    <row r="202" spans="1:30">
+    <row r="202" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>46044</v>
       </c>
@@ -16423,7 +16423,7 @@
         <v>8451.2000000000007</v>
       </c>
     </row>
-    <row r="203" spans="1:30">
+    <row r="203" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>46045</v>
       </c>
@@ -16515,7 +16515,7 @@
         <v>8482.9</v>
       </c>
     </row>
-    <row r="204" spans="1:30">
+    <row r="204" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>46048</v>
       </c>
@@ -16607,7 +16607,7 @@
         <v>8516.6</v>
       </c>
     </row>
-    <row r="205" spans="1:30">
+    <row r="205" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>46049</v>
       </c>
@@ -16699,7 +16699,7 @@
         <v>8482.9</v>
       </c>
     </row>
-    <row r="206" spans="1:30">
+    <row r="206" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>46050</v>
       </c>
@@ -16791,7 +16791,7 @@
         <v>8516.6</v>
       </c>
     </row>
-    <row r="207" spans="1:30">
+    <row r="207" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>46051</v>
       </c>
@@ -16883,7 +16883,7 @@
         <v>8556.6</v>
       </c>
     </row>
-    <row r="208" spans="1:30">
+    <row r="208" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>46052</v>
       </c>
@@ -16975,7 +16975,7 @@
         <v>8652.85</v>
       </c>
     </row>
-    <row r="209" spans="1:30">
+    <row r="209" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>46055</v>
       </c>
@@ -17067,7 +17067,7 @@
         <v>8798.2000000000007</v>
       </c>
     </row>
-    <row r="210" spans="1:30">
+    <row r="210" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>46056</v>
       </c>
@@ -17159,7 +17159,7 @@
         <v>8798.2000000000007</v>
       </c>
     </row>
-    <row r="211" spans="1:30">
+    <row r="211" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>46057</v>
       </c>
@@ -17251,7 +17251,7 @@
         <v>8798.2000000000007</v>
       </c>
     </row>
-    <row r="212" spans="1:30">
+    <row r="212" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>46058</v>
       </c>
@@ -17343,7 +17343,7 @@
         <v>8798.2000000000007</v>
       </c>
     </row>
-    <row r="213" spans="1:30">
+    <row r="213" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>46059</v>
       </c>
@@ -17435,7 +17435,7 @@
         <v>8798.2000000000007</v>
       </c>
     </row>
-    <row r="214" spans="1:30">
+    <row r="214" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>46062</v>
       </c>
@@ -17527,7 +17527,7 @@
         <v>8798.2000000000007</v>
       </c>
     </row>
-    <row r="215" spans="1:30">
+    <row r="215" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>46063</v>
       </c>
@@ -17619,7 +17619,7 @@
         <v>8875.35</v>
       </c>
     </row>
-    <row r="216" spans="1:30">
+    <row r="216" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>46064</v>
       </c>
@@ -17711,7 +17711,7 @@
         <v>8885.9</v>
       </c>
     </row>
-    <row r="217" spans="1:30">
+    <row r="217" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>46065</v>
       </c>
@@ -17803,7 +17803,7 @@
         <v>9058.75</v>
       </c>
     </row>
-    <row r="218" spans="1:30">
+    <row r="218" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>46066</v>
       </c>
@@ -17895,7 +17895,7 @@
         <v>8885.9</v>
       </c>
     </row>
-    <row r="219" spans="1:30">
+    <row r="219" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>46069</v>
       </c>
@@ -17987,7 +17987,7 @@
         <v>9058.75</v>
       </c>
     </row>
-    <row r="220" spans="1:30">
+    <row r="220" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>46070</v>
       </c>
@@ -18079,7 +18079,7 @@
         <v>9273.0499999999993</v>
       </c>
     </row>
-    <row r="221" spans="1:30">
+    <row r="221" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>46071</v>
       </c>
@@ -18171,7 +18171,7 @@
         <v>9436.9</v>
       </c>
     </row>
-    <row r="222" spans="1:30">
+    <row r="222" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>46072</v>
       </c>
@@ -18263,7 +18263,7 @@
         <v>9691.5750000000007</v>
       </c>
     </row>
-    <row r="223" spans="1:30">
+    <row r="223" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>46073</v>
       </c>
@@ -18355,7 +18355,7 @@
         <v>9877.625</v>
       </c>
     </row>
-    <row r="224" spans="1:30">
+    <row r="224" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>46076</v>
       </c>
@@ -18447,7 +18447,7 @@
         <v>9877.625</v>
       </c>
     </row>
-    <row r="225" spans="1:30">
+    <row r="225" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>46077</v>
       </c>
@@ -18539,7 +18539,7 @@
         <v>10102.25</v>
       </c>
     </row>
-    <row r="226" spans="1:30">
+    <row r="226" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>46078</v>
       </c>
@@ -18631,7 +18631,7 @@
         <v>10248.25</v>
       </c>
     </row>
-    <row r="227" spans="1:30">
+    <row r="227" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>46079</v>
       </c>
@@ -18723,7 +18723,7 @@
         <v>10583</v>
       </c>
     </row>
-    <row r="228" spans="1:30">
+    <row r="228" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>46080</v>
       </c>
@@ -18815,7 +18815,7 @@
         <v>10633.9</v>
       </c>
     </row>
-    <row r="229" spans="1:30">
+    <row r="229" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>46083</v>
       </c>
@@ -18907,7 +18907,7 @@
         <v>10633.9</v>
       </c>
     </row>
-    <row r="230" spans="1:30">
+    <row r="230" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>46084</v>
       </c>
@@ -18999,7 +18999,7 @@
         <v>10772.25</v>
       </c>
     </row>
-    <row r="231" spans="1:30">
+    <row r="231" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>46085</v>
       </c>
@@ -19091,7 +19091,7 @@
         <v>10876.900000000001</v>
       </c>
     </row>
-    <row r="232" spans="1:30">
+    <row r="232" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>46086</v>
       </c>
@@ -19183,7 +19183,7 @@
         <v>10876.900000000001</v>
       </c>
     </row>
-    <row r="233" spans="1:30">
+    <row r="233" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>46087</v>
       </c>
@@ -19275,7 +19275,7 @@
         <v>10922.7</v>
       </c>
     </row>
-    <row r="234" spans="1:30">
+    <row r="234" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>46090</v>
       </c>
@@ -19367,7 +19367,7 @@
         <v>10985.099999999999</v>
       </c>
     </row>
-    <row r="235" spans="1:30">
+    <row r="235" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>46091</v>
       </c>
@@ -19459,7 +19459,7 @@
         <v>10985.099999999999</v>
       </c>
     </row>
-    <row r="236" spans="1:30">
+    <row r="236" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>46092</v>
       </c>
@@ -19551,7 +19551,7 @@
         <v>11084.099999999999</v>
       </c>
     </row>
-    <row r="237" spans="1:30">
+    <row r="237" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>46093</v>
       </c>
@@ -19643,7 +19643,7 @@
         <v>11249.65</v>
       </c>
     </row>
-    <row r="238" spans="1:30">
+    <row r="238" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>46094</v>
       </c>
@@ -19735,7 +19735,7 @@
         <v>11249.65</v>
       </c>
     </row>
-    <row r="239" spans="1:30">
+    <row r="239" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>46097</v>
       </c>
@@ -19827,7 +19827,7 @@
         <v>11347.4</v>
       </c>
     </row>
-    <row r="240" spans="1:30">
+    <row r="240" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>46098</v>
       </c>
@@ -19919,7 +19919,7 @@
         <v>11249.65</v>
       </c>
     </row>
-    <row r="241" spans="1:30">
+    <row r="241" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>46099</v>
       </c>
@@ -20011,7 +20011,7 @@
         <v>11249.65</v>
       </c>
     </row>
-    <row r="242" spans="1:30">
+    <row r="242" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>46100</v>
       </c>
@@ -20103,7 +20103,7 @@
         <v>11347.4</v>
       </c>
     </row>
-    <row r="243" spans="1:30">
+    <row r="243" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>46101</v>
       </c>
@@ -20195,7 +20195,7 @@
         <v>11347.4</v>
       </c>
     </row>
-    <row r="244" spans="1:30">
+    <row r="244" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>46104</v>
       </c>
@@ -20287,7 +20287,7 @@
         <v>11347.4</v>
       </c>
     </row>
-    <row r="245" spans="1:30">
+    <row r="245" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>46105</v>
       </c>
@@ -20379,7 +20379,7 @@
         <v>11363.849999999999</v>
       </c>
     </row>
-    <row r="246" spans="1:30">
+    <row r="246" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>46106</v>
       </c>
@@ -20471,7 +20471,7 @@
         <v>11531.099999999999</v>
       </c>
     </row>
-    <row r="247" spans="1:30">
+    <row r="247" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>46107</v>
       </c>
@@ -20563,7 +20563,7 @@
         <v>11531.099999999999</v>
       </c>
     </row>
-    <row r="248" spans="1:30">
+    <row r="248" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>46108</v>
       </c>
@@ -20655,7 +20655,7 @@
         <v>11709.8</v>
       </c>
     </row>
-    <row r="249" spans="1:30">
+    <row r="249" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>46111</v>
       </c>
@@ -20747,7 +20747,7 @@
         <v>11709.8</v>
       </c>
     </row>
-    <row r="250" spans="1:30">
+    <row r="250" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>46112</v>
       </c>
@@ -20839,7 +20839,7 @@
         <v>11709.8</v>
       </c>
     </row>
-    <row r="251" spans="1:30">
+    <row r="251" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>46113</v>
       </c>
@@ -20931,7 +20931,7 @@
         <v>11806.5</v>
       </c>
     </row>
-    <row r="252" spans="1:30">
+    <row r="252" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>46118</v>
       </c>
@@ -21023,7 +21023,7 @@
         <v>11897.55</v>
       </c>
     </row>
-    <row r="253" spans="1:30">
+    <row r="253" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>46119</v>
       </c>
@@ -21115,7 +21115,7 @@
         <v>12104.119999999999</v>
       </c>
     </row>
-    <row r="254" spans="1:30">
+    <row r="254" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>46120</v>
       </c>
@@ -21207,7 +21207,7 @@
         <v>12104.119999999999</v>
       </c>
     </row>
-    <row r="255" spans="1:30">
+    <row r="255" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>46121</v>
       </c>
@@ -21299,7 +21299,7 @@
         <v>12104.119999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:30">
+    <row r="256" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>46122</v>
       </c>
@@ -21391,7 +21391,7 @@
         <v>12104.119999999999</v>
       </c>
     </row>
-    <row r="257" spans="1:30">
+    <row r="257" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>46125</v>
       </c>
@@ -21483,7 +21483,7 @@
         <v>12331.92</v>
       </c>
     </row>
-    <row r="258" spans="1:30">
+    <row r="258" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>46126</v>
       </c>
@@ -21575,7 +21575,7 @@
         <v>12331.92</v>
       </c>
     </row>
-    <row r="259" spans="1:30">
+    <row r="259" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>46127</v>
       </c>
@@ -21667,7 +21667,7 @@
         <v>12565.375</v>
       </c>
     </row>
-    <row r="260" spans="1:30">
+    <row r="260" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>46128</v>
       </c>
@@ -21759,7 +21759,7 @@
         <v>12565.375</v>
       </c>
     </row>
-    <row r="261" spans="1:30">
+    <row r="261" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>46129</v>
       </c>
@@ -21851,7 +21851,7 @@
         <v>12565.375</v>
       </c>
     </row>
-    <row r="262" spans="1:30">
+    <row r="262" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>46132</v>
       </c>
@@ -21943,7 +21943,7 @@
         <v>12565.375</v>
       </c>
     </row>
-    <row r="263" spans="1:30">
+    <row r="263" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>46133</v>
       </c>
@@ -22035,7 +22035,7 @@
         <v>12882.725</v>
       </c>
     </row>
-    <row r="264" spans="1:30">
+    <row r="264" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>46134</v>
       </c>
@@ -22127,7 +22127,7 @@
         <v>13007.6</v>
       </c>
     </row>
-    <row r="265" spans="1:30">
+    <row r="265" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>46135</v>
       </c>
@@ -22219,7 +22219,7 @@
         <v>13345.05</v>
       </c>
     </row>
-    <row r="266" spans="1:30">
+    <row r="266" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>46136</v>
       </c>
@@ -22311,7 +22311,7 @@
         <v>13345.05</v>
       </c>
     </row>
-    <row r="267" spans="1:30">
+    <row r="267" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>46139</v>
       </c>
@@ -22403,7 +22403,7 @@
         <v>13345.05</v>
       </c>
     </row>
-    <row r="268" spans="1:30">
+    <row r="268" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>46140</v>
       </c>
@@ -22495,7 +22495,7 @@
         <v>13340.150000000001</v>
       </c>
     </row>
-    <row r="269" spans="1:30">
+    <row r="269" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>46141</v>
       </c>
@@ -22587,7 +22587,7 @@
         <v>12882.725</v>
       </c>
     </row>
-    <row r="270" spans="1:30">
+    <row r="270" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>46142</v>
       </c>
@@ -22679,7 +22679,7 @@
         <v>12882.725</v>
       </c>
     </row>
-    <row r="271" spans="1:30">
+    <row r="271" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>46146</v>
       </c>
@@ -22771,7 +22771,7 @@
         <v>12882.725</v>
       </c>
     </row>
-    <row r="272" spans="1:30">
+    <row r="272" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>46147</v>
       </c>
@@ -22863,7 +22863,7 @@
         <v>12882.725</v>
       </c>
     </row>
-    <row r="273" spans="1:30">
+    <row r="273" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>46148</v>
       </c>
@@ -22955,7 +22955,7 @@
         <v>13340.150000000001</v>
       </c>
     </row>
-    <row r="274" spans="1:30">
+    <row r="274" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>46149</v>
       </c>
@@ -23047,7 +23047,7 @@
         <v>13340.150000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:30">
+    <row r="275" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>46150</v>
       </c>
@@ -23139,7 +23139,7 @@
         <v>13340.150000000001</v>
       </c>
     </row>
-    <row r="276" spans="1:30">
+    <row r="276" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>46153</v>
       </c>
@@ -23231,7 +23231,7 @@
         <v>13340.150000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:30">
+    <row r="277" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>46154</v>
       </c>
@@ -23323,7 +23323,7 @@
         <v>13701.3</v>
       </c>
     </row>
-    <row r="278" spans="1:30">
+    <row r="278" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>46155</v>
       </c>
@@ -23415,7 +23415,7 @@
         <v>13701.3</v>
       </c>
     </row>
-    <row r="279" spans="1:30">
+    <row r="279" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>46156</v>
       </c>
@@ -23507,7 +23507,7 @@
         <v>13799.6</v>
       </c>
     </row>
-    <row r="280" spans="1:30">
+    <row r="280" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>46157</v>
       </c>
@@ -23599,7 +23599,7 @@
         <v>13701.3</v>
       </c>
     </row>
-    <row r="281" spans="1:30">
+    <row r="281" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>46160</v>
       </c>
@@ -23691,7 +23691,7 @@
         <v>13799.6</v>
       </c>
     </row>
-    <row r="282" spans="1:30">
+    <row r="282" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>46161</v>
       </c>
@@ -23783,7 +23783,7 @@
         <v>13799.6</v>
       </c>
     </row>
-    <row r="283" spans="1:30">
+    <row r="283" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>46162</v>
       </c>
@@ -23875,7 +23875,7 @@
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:30">
+    <row r="284" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>46163</v>
       </c>
@@ -23967,7 +23967,7 @@
         <v>14321.875</v>
       </c>
     </row>
-    <row r="285" spans="1:30">
+    <row r="285" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>46164</v>
       </c>
@@ -24059,7 +24059,7 @@
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="286" spans="1:30">
+    <row r="286" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>46167</v>
       </c>
@@ -24151,7 +24151,7 @@
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:30">
+    <row r="287" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>46168</v>
       </c>
@@ -24243,7 +24243,7 @@
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="288" spans="1:30">
+    <row r="288" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>46169</v>
       </c>
@@ -24335,7 +24335,7 @@
         <v>14321.875</v>
       </c>
     </row>
-    <row r="289" spans="1:30">
+    <row r="289" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>46170</v>
       </c>
@@ -24427,7 +24427,7 @@
         <v>14321.875</v>
       </c>
     </row>
-    <row r="290" spans="1:30">
+    <row r="290" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>46171</v>
       </c>
@@ -24519,7 +24519,7 @@
         <v>14321.875</v>
       </c>
     </row>
-    <row r="291" spans="1:30">
+    <row r="291" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>46174</v>
       </c>
@@ -24611,7 +24611,7 @@
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="292" spans="1:30">
+    <row r="292" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>46175</v>
       </c>
@@ -24703,7 +24703,7 @@
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="293" spans="1:30">
+    <row r="293" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>46176</v>
       </c>
@@ -24795,7 +24795,7 @@
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="294" spans="1:30">
+    <row r="294" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>46177</v>
       </c>
@@ -24887,7 +24887,7 @@
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="295" spans="1:30">
+    <row r="295" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>46178</v>
       </c>
@@ -24979,7 +24979,7 @@
         <v>14321.875</v>
       </c>
     </row>
-    <row r="296" spans="1:30">
+    <row r="296" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>46181</v>
       </c>
@@ -25071,7 +25071,7 @@
         <v>14321.875</v>
       </c>
     </row>
-    <row r="297" spans="1:30">
+    <row r="297" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>46182</v>
       </c>
@@ -25163,7 +25163,7 @@
         <v>14321.875</v>
       </c>
     </row>
-    <row r="298" spans="1:30">
+    <row r="298" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>46183</v>
       </c>
@@ -25255,7 +25255,7 @@
         <v>14321.875</v>
       </c>
     </row>
-    <row r="299" spans="1:30">
+    <row r="299" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>46184</v>
       </c>
@@ -25347,7 +25347,7 @@
         <v>14321.875</v>
       </c>
     </row>
-    <row r="300" spans="1:30">
+    <row r="300" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>46185</v>
       </c>
@@ -25439,7 +25439,7 @@
         <v>14550.474999999999</v>
       </c>
     </row>
-    <row r="301" spans="1:30">
+    <row r="301" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>46188</v>
       </c>
@@ -25531,7 +25531,7 @@
         <v>14550.474999999999</v>
       </c>
     </row>
-    <row r="302" spans="1:30">
+    <row r="302" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>46189</v>
       </c>
@@ -25623,7 +25623,7 @@
         <v>14550.474999999999</v>
       </c>
     </row>
-    <row r="303" spans="1:30">
+    <row r="303" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>46190</v>
       </c>
@@ -25715,7 +25715,7 @@
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="304" spans="1:30">
+    <row r="304" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>46191</v>
       </c>
@@ -25807,7 +25807,7 @@
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="305" spans="1:30">
+    <row r="305" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>46192</v>
       </c>
@@ -25899,7 +25899,7 @@
         <v>14550.474999999999</v>
       </c>
     </row>
-    <row r="306" spans="1:30">
+    <row r="306" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>46195</v>
       </c>
@@ -25991,7 +25991,7 @@
         <v>14550.474999999999</v>
       </c>
     </row>
-    <row r="307" spans="1:30">
+    <row r="307" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>46196</v>
       </c>
@@ -26083,7 +26083,7 @@
         <v>14321.875</v>
       </c>
     </row>
-    <row r="308" spans="1:30">
+    <row r="308" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>46197</v>
       </c>
@@ -26175,7 +26175,7 @@
         <v>14321.875</v>
       </c>
     </row>
-    <row r="309" spans="1:30">
+    <row r="309" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>46198</v>
       </c>
@@ -26267,7 +26267,7 @@
         <v>14321.875</v>
       </c>
     </row>
-    <row r="310" spans="1:30">
+    <row r="310" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>46199</v>
       </c>
@@ -26359,7 +26359,7 @@
         <v>14550.474999999999</v>
       </c>
     </row>
-    <row r="311" spans="1:30">
+    <row r="311" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>46203</v>
       </c>
@@ -26451,7 +26451,7 @@
         <v>14550.474999999999</v>
       </c>
     </row>
-    <row r="312" spans="1:30">
+    <row r="312" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>46204</v>
       </c>
@@ -26543,7 +26543,7 @@
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="313" spans="1:30">
+    <row r="313" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>46205</v>
       </c>
@@ -26635,7 +26635,7 @@
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="314" spans="1:30">
+    <row r="314" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>46206</v>
       </c>
@@ -26727,7 +26727,7 @@
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="315" spans="1:30">
+    <row r="315" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>46209</v>
       </c>
@@ -26819,7 +26819,7 @@
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="316" spans="1:30">
+    <row r="316" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>46210</v>
       </c>
@@ -26911,7 +26911,7 @@
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="317" spans="1:30">
+    <row r="317" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>46211</v>
       </c>
@@ -27003,7 +27003,7 @@
         <v>15026.974999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:30">
+    <row r="318" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>46212</v>
       </c>
@@ -27095,7 +27095,7 @@
         <v>15026.974999999999</v>
       </c>
     </row>
-    <row r="319" spans="1:30">
+    <row r="319" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>46213</v>
       </c>
@@ -27187,7 +27187,7 @@
         <v>15205.65</v>
       </c>
     </row>
-    <row r="320" spans="1:30">
+    <row r="320" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>46216</v>
       </c>
@@ -27279,7 +27279,7 @@
         <v>15370.55</v>
       </c>
     </row>
-    <row r="321" spans="1:30">
+    <row r="321" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>46217</v>
       </c>
@@ -27371,7 +27371,7 @@
         <v>15799.95</v>
       </c>
     </row>
-    <row r="322" spans="1:30">
+    <row r="322" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>46218</v>
       </c>
@@ -27463,7 +27463,7 @@
         <v>15799.95</v>
       </c>
     </row>
-    <row r="323" spans="1:30">
+    <row r="323" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>46219</v>
       </c>
@@ -27555,7 +27555,7 @@
         <v>16223.75</v>
       </c>
     </row>
-    <row r="324" spans="1:30">
+    <row r="324" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>46220</v>
       </c>
@@ -27647,7 +27647,7 @@
         <v>15805.400000000001</v>
       </c>
     </row>
-    <row r="325" spans="1:30">
+    <row r="325" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>46223</v>
       </c>
@@ -27739,7 +27739,7 @@
         <v>15805.400000000001</v>
       </c>
     </row>
-    <row r="326" spans="1:30">
+    <row r="326" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>46224</v>
       </c>
@@ -27831,7 +27831,7 @@
         <v>15805.400000000001</v>
       </c>
     </row>
-    <row r="327" spans="1:30">
+    <row r="327" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>46225</v>
       </c>
@@ -27923,7 +27923,7 @@
         <v>15370.55</v>
       </c>
     </row>
-    <row r="328" spans="1:30">
+    <row r="328" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>46227</v>
       </c>
@@ -28015,7 +28015,7 @@
         <v>15205.65</v>
       </c>
     </row>
-    <row r="329" spans="1:30">
+    <row r="329" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>46230</v>
       </c>
@@ -28107,7 +28107,7 @@
         <v>15370.55</v>
       </c>
     </row>
-    <row r="330" spans="1:30">
+    <row r="330" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>46233</v>
       </c>
@@ -28199,7 +28199,7 @@
         <v>15370.55</v>
       </c>
     </row>
-    <row r="331" spans="1:30">
+    <row r="331" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>46234</v>
       </c>
@@ -28291,7 +28291,7 @@
         <v>15805.400000000001</v>
       </c>
     </row>
-    <row r="332" spans="1:30">
+    <row r="332" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>46237</v>
       </c>
@@ -28383,7 +28383,7 @@
         <v>16021.7</v>
       </c>
     </row>
-    <row r="333" spans="1:30">
+    <row r="333" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>46238</v>
       </c>
@@ -28475,7 +28475,7 @@
         <v>15597.900000000001</v>
       </c>
     </row>
-    <row r="334" spans="1:30">
+    <row r="334" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>46239</v>
       </c>
@@ -28567,7 +28567,7 @@
         <v>15370.55</v>
       </c>
     </row>
-    <row r="335" spans="1:30">
+    <row r="335" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>46241</v>
       </c>
@@ -28659,7 +28659,7 @@
         <v>15370.55</v>
       </c>
     </row>
-    <row r="336" spans="1:30">
+    <row r="336" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>46244</v>
       </c>
@@ -28751,7 +28751,7 @@
         <v>15319.65</v>
       </c>
     </row>
-    <row r="337" spans="1:30">
+    <row r="337" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>46245</v>
       </c>
@@ -28843,7 +28843,7 @@
         <v>15213.34</v>
       </c>
     </row>
-    <row r="338" spans="1:30">
+    <row r="338" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>46246</v>
       </c>
@@ -28935,7 +28935,7 @@
         <v>15213.34</v>
       </c>
     </row>
-    <row r="339" spans="1:30">
+    <row r="339" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>46247</v>
       </c>
@@ -29027,7 +29027,7 @@
         <v>15213.34</v>
       </c>
     </row>
-    <row r="340" spans="1:30">
+    <row r="340" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>46248</v>
       </c>
@@ -29119,7 +29119,7 @@
         <v>15213.34</v>
       </c>
     </row>
-    <row r="341" spans="1:30">
+    <row r="341" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>46251</v>
       </c>
@@ -29211,7 +29211,7 @@
         <v>15213.34</v>
       </c>
     </row>
-    <row r="342" spans="1:30">
+    <row r="342" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>46252</v>
       </c>
@@ -29303,7 +29303,7 @@
         <v>15319.65</v>
       </c>
     </row>
-    <row r="343" spans="1:30">
+    <row r="343" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>46253</v>
       </c>
@@ -29395,7 +29395,7 @@
         <v>15319.65</v>
       </c>
     </row>
-    <row r="344" spans="1:30">
+    <row r="344" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>46254</v>
       </c>
@@ -29487,7 +29487,7 @@
         <v>15319.65</v>
       </c>
     </row>
-    <row r="345" spans="1:30">
+    <row r="345" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>46255</v>
       </c>
@@ -29579,7 +29579,7 @@
         <v>15319.65</v>
       </c>
     </row>
-    <row r="346" spans="1:30">
+    <row r="346" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>46258</v>
       </c>
@@ -29671,7 +29671,7 @@
         <v>15213.34</v>
       </c>
     </row>
-    <row r="347" spans="1:30">
+    <row r="347" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>46259</v>
       </c>
@@ -29763,7 +29763,7 @@
         <v>15099.34</v>
       </c>
     </row>
-    <row r="348" spans="1:30">
+    <row r="348" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>46260</v>
       </c>
@@ -29855,7 +29855,7 @@
         <v>15099.34</v>
       </c>
     </row>
-    <row r="349" spans="1:30">
+    <row r="349" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>46261</v>
       </c>
@@ -29947,7 +29947,7 @@
         <v>15213.34</v>
       </c>
     </row>
-    <row r="350" spans="1:30">
+    <row r="350" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>46262</v>
       </c>
@@ -30039,7 +30039,7 @@
         <v>15099.34</v>
       </c>
     </row>
-    <row r="351" spans="1:30">
+    <row r="351" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>46265</v>
       </c>
@@ -30131,7 +30131,7 @@
         <v>15099.34</v>
       </c>
     </row>
-    <row r="352" spans="1:30">
+    <row r="352" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>46266</v>
       </c>
@@ -30223,7 +30223,7 @@
         <v>15026.974999999999</v>
       </c>
     </row>
-    <row r="353" spans="1:30">
+    <row r="353" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>46267</v>
       </c>
@@ -30315,7 +30315,7 @@
         <v>15026.974999999999</v>
       </c>
     </row>
-    <row r="354" spans="1:30">
+    <row r="354" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>46268</v>
       </c>
@@ -30407,7 +30407,7 @@
         <v>15099.34</v>
       </c>
     </row>
-    <row r="355" spans="1:30">
+    <row r="355" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>46269</v>
       </c>
@@ -30499,7 +30499,7 @@
         <v>15026.974999999999</v>
       </c>
     </row>
-    <row r="356" spans="1:30">
+    <row r="356" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>46272</v>
       </c>
@@ -30591,7 +30591,7 @@
         <v>15026.974999999999</v>
       </c>
     </row>
-    <row r="357" spans="1:30">
+    <row r="357" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>46273</v>
       </c>
@@ -30601,8 +30601,8 @@
       <c r="C357">
         <v>151585431.25</v>
       </c>
-      <c r="D357" t="s">
-        <v>23</v>
+      <c r="D357">
+        <v>547</v>
       </c>
       <c r="E357">
         <v>5617.8</v>
@@ -30683,7 +30683,7 @@
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="358" spans="1:30">
+    <row r="358" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>46274</v>
       </c>
@@ -30693,8 +30693,8 @@
       <c r="C358">
         <v>151577894.56999999</v>
       </c>
-      <c r="D358" t="s">
-        <v>23</v>
+      <c r="D358">
+        <v>547</v>
       </c>
       <c r="E358">
         <v>4042.08</v>
@@ -30745,7 +30745,7 @@
         <v>5.712244644311415E-2</v>
       </c>
       <c r="U358">
-        <v>112.36</v>
+        <v>112.28</v>
       </c>
       <c r="V358">
         <v>-1.202325002151261</v>
@@ -30754,16 +30754,16 @@
         <v>-3.9109511967821864</v>
       </c>
       <c r="X358" s="3">
-        <v>2.5663730780007832E-3</v>
+        <v>1.8525486756668652E-3</v>
       </c>
       <c r="Y358" s="3">
-        <v>3.965724481886812E-3</v>
+        <v>3.9426978882631369E-3</v>
       </c>
       <c r="Z358" s="3">
-        <v>3.3576927728046434E-3</v>
+        <v>3.3457956994324117E-3</v>
       </c>
       <c r="AA358" s="3">
-        <v>4.3180641782115574E-3</v>
+        <v>4.3140984870874803E-3</v>
       </c>
       <c r="AB358">
         <v>10691.205</v>
@@ -30775,7 +30775,7 @@
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="359" spans="1:30">
+    <row r="359" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>46275</v>
       </c>
@@ -30785,8 +30785,11 @@
       <c r="C359">
         <v>151268122.44999999</v>
       </c>
-      <c r="D359" t="s">
-        <v>23</v>
+      <c r="D359">
+        <v>547</v>
+      </c>
+      <c r="E359">
+        <v>6322.8</v>
       </c>
       <c r="F359">
         <v>2</v>
@@ -30834,7 +30837,7 @@
         <v>6.0696652499836468E-2</v>
       </c>
       <c r="U359">
-        <v>112.36</v>
+        <v>112.91</v>
       </c>
       <c r="V359">
         <v>-1.4042328439257012</v>
@@ -30843,25 +30846,114 @@
         <v>-3.9109511967821864</v>
       </c>
       <c r="X359" s="3">
-        <v>4.6194633724692125E-3</v>
+        <v>9.5370559753069628E-3</v>
       </c>
       <c r="Y359" s="3">
-        <v>3.9989053386227684E-3</v>
+        <v>4.1345107644454723E-3</v>
       </c>
       <c r="Z359" s="3">
-        <v>3.4320731526877148E-3</v>
+        <v>3.5021359560294452E-3</v>
       </c>
       <c r="AA359" s="3">
-        <v>4.3367394871025337E-3</v>
+        <v>4.3600937548831107E-3</v>
       </c>
       <c r="AB359">
-        <v>10628.95</v>
+        <v>10365.225</v>
       </c>
       <c r="AC359">
-        <v>10639.13</v>
+        <v>10634.04</v>
       </c>
       <c r="AD359">
-        <v>14610.8</v>
+        <v>14583.625</v>
+      </c>
+    </row>
+    <row r="360" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A360" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B360">
+        <v>111.71193594</v>
+      </c>
+      <c r="C360">
+        <v>151090393.34999999</v>
+      </c>
+      <c r="D360" t="s">
+        <v>23</v>
+      </c>
+      <c r="E360">
+        <v>7537.5</v>
+      </c>
+      <c r="G360">
+        <v>6.3783403807000001</v>
+      </c>
+      <c r="H360">
+        <v>5.8374819599999999</v>
+      </c>
+      <c r="I360">
+        <v>183.51</v>
+      </c>
+      <c r="J360">
+        <v>6.43</v>
+      </c>
+      <c r="K360">
+        <v>5.87</v>
+      </c>
+      <c r="L360">
+        <v>11.711935939999996</v>
+      </c>
+      <c r="M360">
+        <v>12.173356537891378</v>
+      </c>
+      <c r="N360">
+        <v>6.5781908599999985</v>
+      </c>
+      <c r="O360">
+        <v>6.5699999999999994</v>
+      </c>
+      <c r="P360">
+        <v>4.8814061934728432E-3</v>
+      </c>
+      <c r="Q360">
+        <v>4.0571304213934505E-3</v>
+      </c>
+      <c r="R360">
+        <v>0.10888695932742611</v>
+      </c>
+      <c r="S360">
+        <v>2.997226059736624E-2</v>
+      </c>
+      <c r="T360">
+        <v>6.3098983453979685E-2</v>
+      </c>
+      <c r="U360">
+        <v>112.91</v>
+      </c>
+      <c r="V360">
+        <v>-1.5200757307032076</v>
+      </c>
+      <c r="W360">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="X360" s="3">
+        <v>1.072458417194988E-2</v>
+      </c>
+      <c r="Y360" s="3">
+        <v>4.4315942918622007E-3</v>
+      </c>
+      <c r="Z360" s="3">
+        <v>3.6025729686688084E-3</v>
+      </c>
+      <c r="AA360" s="3">
+        <v>4.4165622050194777E-3</v>
+      </c>
+      <c r="AB360">
+        <v>10365.225</v>
+      </c>
+      <c r="AC360">
+        <v>10576.775000000001</v>
+      </c>
+      <c r="AD360">
+        <v>14583.625</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Data-ETFPESOV.xlsx
+++ b/Data/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACF7903-26FA-4BAE-A813-D53DE119A5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D730ED-B221-491E-A12D-34186FF9286B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -515,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AD360"/>
+  <dimension ref="A1:AD361"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="24" max="27" width="11.5546875" style="3"/>
@@ -30877,12 +30877,15 @@
       <c r="C360">
         <v>151090393.34999999</v>
       </c>
-      <c r="D360" t="s">
-        <v>23</v>
+      <c r="D360">
+        <v>547</v>
       </c>
       <c r="E360">
         <v>7537.5</v>
       </c>
+      <c r="F360">
+        <v>2</v>
+      </c>
       <c r="G360">
         <v>6.3783403807000001</v>
       </c>
@@ -30926,7 +30929,7 @@
         <v>6.3098983453979685E-2</v>
       </c>
       <c r="U360">
-        <v>112.91</v>
+        <v>112.5</v>
       </c>
       <c r="V360">
         <v>-1.5200757307032076</v>
@@ -30935,16 +30938,16 @@
         <v>-3.9109511967821864</v>
       </c>
       <c r="X360" s="3">
-        <v>1.072458417194988E-2</v>
+        <v>7.0544302483779298E-3</v>
       </c>
       <c r="Y360" s="3">
-        <v>4.4315942918622007E-3</v>
+        <v>4.3132022298114922E-3</v>
       </c>
       <c r="Z360" s="3">
-        <v>3.6025729686688084E-3</v>
+        <v>3.541403736609276E-3</v>
       </c>
       <c r="AA360" s="3">
-        <v>4.4165622050194777E-3</v>
+        <v>4.3961724609996337E-3</v>
       </c>
       <c r="AB360">
         <v>10365.225</v>
@@ -30954,6 +30957,95 @@
       </c>
       <c r="AD360">
         <v>14583.625</v>
+      </c>
+    </row>
+    <row r="361" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A361" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B361">
+        <v>111.47437478000001</v>
+      </c>
+      <c r="C361">
+        <v>150769091.88999999</v>
+      </c>
+      <c r="D361" t="s">
+        <v>23</v>
+      </c>
+      <c r="F361">
+        <v>6</v>
+      </c>
+      <c r="G361">
+        <v>6.3641696084999992</v>
+      </c>
+      <c r="H361">
+        <v>5.8769270654000003</v>
+      </c>
+      <c r="I361">
+        <v>183.12</v>
+      </c>
+      <c r="J361">
+        <v>6.41</v>
+      </c>
+      <c r="K361">
+        <v>5.91</v>
+      </c>
+      <c r="L361">
+        <v>11.474374779999996</v>
+      </c>
+      <c r="M361">
+        <v>11.934962940540949</v>
+      </c>
+      <c r="N361">
+        <v>6.5768998599999993</v>
+      </c>
+      <c r="O361">
+        <v>6.5699999999999994</v>
+      </c>
+      <c r="P361">
+        <v>4.853463195651336E-3</v>
+      </c>
+      <c r="Q361">
+        <v>4.0457201142888354E-3</v>
+      </c>
+      <c r="R361">
+        <v>0.10888652462370721</v>
+      </c>
+      <c r="S361">
+        <v>2.8491151675003046E-2</v>
+      </c>
+      <c r="T361">
+        <v>5.9437950532514883E-2</v>
+      </c>
+      <c r="U361">
+        <v>112.5</v>
+      </c>
+      <c r="V361">
+        <v>-1.7294983393910668</v>
+      </c>
+      <c r="W361">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="X361" s="3">
+        <v>9.2005469599996115E-3</v>
+      </c>
+      <c r="Y361" s="3">
+        <v>4.4455868742121303E-3</v>
+      </c>
+      <c r="Z361" s="3">
+        <v>3.6334095085302277E-3</v>
+      </c>
+      <c r="AA361" s="3">
+        <v>4.4334181217329629E-3</v>
+      </c>
+      <c r="AB361">
+        <v>10101.5</v>
+      </c>
+      <c r="AC361">
+        <v>10524.6</v>
+      </c>
+      <c r="AD361">
+        <v>14556.45</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Data-ETFPESOV.xlsx
+++ b/Data/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D730ED-B221-491E-A12D-34186FF9286B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCCF520-53B6-4CA3-8FC5-11D0B2C1D5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -515,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AD361"/>
+  <dimension ref="A1:AD362"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="24" max="27" width="11.5546875" style="3"/>
@@ -30969,8 +30969,11 @@
       <c r="C361">
         <v>150769091.88999999</v>
       </c>
-      <c r="D361" t="s">
-        <v>23</v>
+      <c r="D361">
+        <v>547</v>
+      </c>
+      <c r="E361">
+        <v>13701.18</v>
       </c>
       <c r="F361">
         <v>6</v>
@@ -31018,7 +31021,7 @@
         <v>5.9437950532514883E-2</v>
       </c>
       <c r="U361">
-        <v>112.5</v>
+        <v>112.3</v>
       </c>
       <c r="V361">
         <v>-1.7294983393910668</v>
@@ -31027,24 +31030,113 @@
         <v>-3.9109511967821864</v>
       </c>
       <c r="X361" s="3">
-        <v>9.2005469599996115E-3</v>
+        <v>7.406412654292982E-3</v>
       </c>
       <c r="Y361" s="3">
-        <v>4.4455868742121303E-3</v>
+        <v>4.3877115740280455E-3</v>
       </c>
       <c r="Z361" s="3">
-        <v>3.6334095085302277E-3</v>
+        <v>3.603507270101784E-3</v>
       </c>
       <c r="AA361" s="3">
-        <v>4.4334181217329629E-3</v>
+        <v>4.4234507089234813E-3</v>
       </c>
       <c r="AB361">
+        <v>10365.225</v>
+      </c>
+      <c r="AC361">
+        <v>10576.775000000001</v>
+      </c>
+      <c r="AD361">
+        <v>14523.3</v>
+      </c>
+    </row>
+    <row r="362" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A362" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B362">
+        <v>111.32416256</v>
+      </c>
+      <c r="C362">
+        <v>150565929.87</v>
+      </c>
+      <c r="D362" t="s">
+        <v>23</v>
+      </c>
+      <c r="F362">
+        <v>3</v>
+      </c>
+      <c r="G362">
+        <v>6.3617192194000012</v>
+      </c>
+      <c r="H362">
+        <v>5.9064669940999996</v>
+      </c>
+      <c r="I362">
+        <v>182.88</v>
+      </c>
+      <c r="J362">
+        <v>6.41</v>
+      </c>
+      <c r="K362">
+        <v>5.94</v>
+      </c>
+      <c r="L362">
+        <v>11.324162559999994</v>
+      </c>
+      <c r="M362">
+        <v>11.78825918832529</v>
+      </c>
+      <c r="N362">
+        <v>6.5787812800000003</v>
+      </c>
+      <c r="O362">
+        <v>6.5699999999999994</v>
+      </c>
+      <c r="P362">
+        <v>4.8766637316186119E-3</v>
+      </c>
+      <c r="Q362">
+        <v>4.0596452461012806E-3</v>
+      </c>
+      <c r="R362">
+        <v>0.10888658800143597</v>
+      </c>
+      <c r="S362">
+        <v>4.3416150734532089E-2</v>
+      </c>
+      <c r="T362">
+        <v>6.2594045869202031E-2</v>
+      </c>
+      <c r="U362">
+        <v>112.3</v>
+      </c>
+      <c r="V362">
+        <v>-1.8619182811407842</v>
+      </c>
+      <c r="W362">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="X362" s="3">
+        <v>8.7657289986264875E-3</v>
+      </c>
+      <c r="Y362" s="3">
+        <v>4.6414089038265254E-3</v>
+      </c>
+      <c r="Z362" s="3">
+        <v>3.7260779635504395E-3</v>
+      </c>
+      <c r="AA362" s="3">
+        <v>4.4138396586395996E-3</v>
+      </c>
+      <c r="AB362">
         <v>10101.5</v>
       </c>
-      <c r="AC361">
-        <v>10524.6</v>
-      </c>
-      <c r="AD361">
+      <c r="AC362">
+        <v>10628.95</v>
+      </c>
+      <c r="AD362">
         <v>14556.45</v>
       </c>
     </row>

--- a/Data/Data-ETFPESOV.xlsx
+++ b/Data/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCCF520-53B6-4CA3-8FC5-11D0B2C1D5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7681B8A5-57DC-4E86-AD84-63E9C9FE731F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -515,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AD362"/>
+  <dimension ref="A1:AD363"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="24" max="27" width="11.5546875" style="3"/>
@@ -31061,8 +31061,11 @@
       <c r="C362">
         <v>150565929.87</v>
       </c>
-      <c r="D362" t="s">
-        <v>23</v>
+      <c r="D362">
+        <v>547</v>
+      </c>
+      <c r="E362">
+        <v>55472.5</v>
       </c>
       <c r="F362">
         <v>3</v>
@@ -31110,7 +31113,7 @@
         <v>6.2594045869202031E-2</v>
       </c>
       <c r="U362">
-        <v>112.3</v>
+        <v>112.52</v>
       </c>
       <c r="V362">
         <v>-1.8619182811407842</v>
@@ -31119,24 +31122,113 @@
         <v>-3.9109511967821864</v>
       </c>
       <c r="X362" s="3">
-        <v>8.7657289986264875E-3</v>
+        <v>1.0741939687670898E-2</v>
       </c>
       <c r="Y362" s="3">
-        <v>4.6414089038265254E-3</v>
+        <v>4.7051576357311836E-3</v>
       </c>
       <c r="Z362" s="3">
-        <v>3.7260779635504395E-3</v>
+        <v>3.7590148083678459E-3</v>
       </c>
       <c r="AA362" s="3">
-        <v>4.4138396586395996E-3</v>
+        <v>4.4248186069120688E-3</v>
       </c>
       <c r="AB362">
+        <v>10365.225</v>
+      </c>
+      <c r="AC362">
+        <v>10634.04</v>
+      </c>
+      <c r="AD362">
+        <v>14583.625</v>
+      </c>
+    </row>
+    <row r="363" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A363" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B363">
+        <v>111.0322398</v>
+      </c>
+      <c r="C363">
+        <v>150171104.33000001</v>
+      </c>
+      <c r="D363" t="s">
+        <v>23</v>
+      </c>
+      <c r="F363">
+        <v>1</v>
+      </c>
+      <c r="G363">
+        <v>6.3691826865000003</v>
+      </c>
+      <c r="H363">
+        <v>5.9100017074000002</v>
+      </c>
+      <c r="I363">
+        <v>182.88</v>
+      </c>
+      <c r="J363">
+        <v>6.41</v>
+      </c>
+      <c r="K363">
+        <v>5.94</v>
+      </c>
+      <c r="L363">
+        <v>11.03223980000001</v>
+      </c>
+      <c r="M363">
+        <v>11.78825918832529</v>
+      </c>
+      <c r="N363">
+        <v>6.5799791199999991</v>
+      </c>
+      <c r="O363">
+        <v>6.5699999999999994</v>
+      </c>
+      <c r="P363">
+        <v>4.7028467483318785E-2</v>
+      </c>
+      <c r="Q363">
+        <v>3.3933928961874957E-2</v>
+      </c>
+      <c r="R363">
+        <v>0.11060754078161893</v>
+      </c>
+      <c r="S363">
+        <v>0.30054235834682252</v>
+      </c>
+      <c r="T363">
+        <v>0.32755468437867252</v>
+      </c>
+      <c r="U363">
+        <v>112.52</v>
+      </c>
+      <c r="V363">
+        <v>-2.1192634883058004</v>
+      </c>
+      <c r="W363">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="X363" s="3">
+        <v>1.3399353221009269E-2</v>
+      </c>
+      <c r="Y363" s="3">
+        <v>5.077582794241144E-3</v>
+      </c>
+      <c r="Z363" s="3">
+        <v>3.9683587845192863E-3</v>
+      </c>
+      <c r="AA363" s="3">
+        <v>4.4793643999260346E-3</v>
+      </c>
+      <c r="AB363">
         <v>10101.5</v>
       </c>
-      <c r="AC362">
+      <c r="AC363">
         <v>10628.95</v>
       </c>
-      <c r="AD362">
+      <c r="AD363">
         <v>14556.45</v>
       </c>
     </row>

--- a/Data/Data-ETFPESOV.xlsx
+++ b/Data/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7681B8A5-57DC-4E86-AD84-63E9C9FE731F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFCCACA-0B55-4983-B6D4-7346C665877D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Fecha</t>
   </si>
@@ -515,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AD363"/>
+  <dimension ref="A1:AD364"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="24" max="27" width="11.5546875" style="3"/>
@@ -31156,6 +31156,9 @@
       <c r="D363" t="s">
         <v>23</v>
       </c>
+      <c r="E363">
+        <v>3384</v>
+      </c>
       <c r="F363">
         <v>1</v>
       </c>
@@ -31202,7 +31205,7 @@
         <v>0.32755468437867252</v>
       </c>
       <c r="U363">
-        <v>112.52</v>
+        <v>112.8</v>
       </c>
       <c r="V363">
         <v>-2.1192634883058004</v>
@@ -31211,25 +31214,114 @@
         <v>-3.9109511967821864</v>
       </c>
       <c r="X363" s="3">
-        <v>1.3399353221009269E-2</v>
+        <v>1.5921143293013085E-2</v>
       </c>
       <c r="Y363" s="3">
-        <v>5.077582794241144E-3</v>
+        <v>5.1589308610799764E-3</v>
       </c>
       <c r="Z363" s="3">
-        <v>3.9683587845192863E-3</v>
+        <v>4.0103886190526834E-3</v>
       </c>
       <c r="AA363" s="3">
-        <v>4.4793643999260346E-3</v>
+        <v>4.4933743447705E-3</v>
       </c>
       <c r="AB363">
-        <v>10101.5</v>
+        <v>10047.755000000001</v>
       </c>
       <c r="AC363">
+        <v>10576.775000000001</v>
+      </c>
+      <c r="AD363">
+        <v>14523.3</v>
+      </c>
+    </row>
+    <row r="364" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A364" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B364">
+        <v>111.09142332</v>
+      </c>
+      <c r="C364">
+        <v>150251150.05000001</v>
+      </c>
+      <c r="D364" t="s">
+        <v>23</v>
+      </c>
+      <c r="F364">
+        <v>1</v>
+      </c>
+      <c r="G364">
+        <v>6.3601379445572119</v>
+      </c>
+      <c r="H364">
+        <v>5.9632087408568673</v>
+      </c>
+      <c r="I364">
+        <v>182.51</v>
+      </c>
+      <c r="J364">
+        <v>6.4</v>
+      </c>
+      <c r="K364">
+        <v>5.99</v>
+      </c>
+      <c r="L364">
+        <v>11.091423319999993</v>
+      </c>
+      <c r="M364">
+        <v>11.562090903659495</v>
+      </c>
+      <c r="N364">
+        <v>6.5790034357287368</v>
+      </c>
+      <c r="O364">
+        <v>6.5699999999999994</v>
+      </c>
+      <c r="P364">
+        <v>6.6992483992895729E-2</v>
+      </c>
+      <c r="Q364">
+        <v>4.783553059903891E-2</v>
+      </c>
+      <c r="R364">
+        <v>0.11226532309381644</v>
+      </c>
+      <c r="S364">
+        <v>5.0394769067740874E-2</v>
+      </c>
+      <c r="T364">
+        <v>7.710227115416135E-2</v>
+      </c>
+      <c r="U364">
+        <v>112.8</v>
+      </c>
+      <c r="V364">
+        <v>-2.0670901147217924</v>
+      </c>
+      <c r="W364">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="X364" s="3">
+        <v>1.5379915289035484E-2</v>
+      </c>
+      <c r="Y364" s="3">
+        <v>5.6449252352799295E-3</v>
+      </c>
+      <c r="Z364" s="3">
+        <v>4.1842846656368502E-3</v>
+      </c>
+      <c r="AA364" s="3">
+        <v>4.553490847039301E-3</v>
+      </c>
+      <c r="AB364">
+        <v>9994.01</v>
+      </c>
+      <c r="AC364">
         <v>10628.95</v>
       </c>
-      <c r="AD363">
-        <v>14556.45</v>
+      <c r="AD364">
+        <v>14490.15</v>
       </c>
     </row>
   </sheetData>
